--- a/[NEST 19기] MINI IR DAY 참여팀 정보 (공유용).xlsx
+++ b/[NEST 19기] MINI IR DAY 참여팀 정보 (공유용).xlsx
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>포레스트잘란</t>
+          <t>한국금융투자</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>한국금융투자</t>
+          <t>포레스트잘란</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">

--- a/[NEST 19기] MINI IR DAY 참여팀 정보 (공유용).xlsx
+++ b/[NEST 19기] MINI IR DAY 참여팀 정보 (공유용).xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="3.88" customWidth="1" style="24" min="5" max="5"/>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>레이어랩</t>
+          <t>로테아</t>
         </is>
       </c>
       <c r="G8" s="14" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>로테아</t>
+          <t>비브라보</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -1376,25 +1376,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>비브라보</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="n">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>레이어랩</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="C16" s="14" t="n">
         <v>0.7569444444444444</v>
       </c>
-      <c r="I16" s="16" t="n">
-        <v>20</v>
-      </c>
-    </row>
+      <c r="D16" s="16" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
